--- a/운동프로그램_주6일분할_v21.xlsx
+++ b/운동프로그램_주6일분할_v21.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4100" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED1E0494-1DBB-43B2-8F29-296D9E00630C}"/>
+  <xr:revisionPtr revIDLastSave="4105" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB5E3654-5E14-4600-9749-F2FA60EC8F67}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="7" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5142,9 +5142,6 @@
     <t>시티드 레그 컬</t>
   </si>
   <si>
-    <t>옆 센터로 이동(약 3분) 후. 고관절이 굽어 햄스트링이 늘어난 구간.</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -5787,9 +5784,6 @@
     <t>사두</t>
   </si>
   <si>
-    <t>라잉 레그 컬 4 · 루마니안 3 · 원 레그 라잉 컬 3 · 시티드 레그 컬 4</t>
-  </si>
-  <si>
     <t>후면삼각</t>
   </si>
   <si>
@@ -7039,7 +7033,15 @@
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>월~토 · 일요일 휴식 · 원본 Downloads\주6일_분할_프로그램.md + 월요일 트랩바 슈러그 3 · 불가리안(상체 숙여서) 3 · 레그 익스텐션 3→2 · 복귀판(v20)은 그대로 두고 한 달 뒤 돌아간다</t>
+    <t>옆 센터로 이동(약 3분) 후. 고관절이 굽어 햄스트링이 늘어난 구간. [2026-10-29 사용자 결정] 4 → 3 — 금요일 하체 부담 덜기(햄스트링 금 10 → 9).</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>라잉 레그 컬 4 · 루마니안 3 · 원 레그 라잉 컬 3 · 시티드 레그 컬 3</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>월~토 · 일요일 휴식 · 원본 Downloads\주6일_분할_프로그램.md + 월요일 트랩바 슈러그 3 · 불가리안(상체 숙여서) 3 · 레그 익스텐션 3→2 · 복귀판(v20)은 그대로 두고 한 달 뒤 돌아간다 · 금요일 시티드 레그 컬 4→3</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
 </sst>
@@ -16360,7 +16362,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.75">
       <c r="A1" s="117" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -16373,19 +16375,19 @@
         <v>891</v>
       </c>
       <c r="B4" s="99" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="C4" s="99" t="s">
         <v>148</v>
       </c>
       <c r="D4" s="99" t="s">
+        <v>1224</v>
+      </c>
+      <c r="E4" s="99" t="s">
         <v>1225</v>
       </c>
-      <c r="E4" s="99" t="s">
+      <c r="F4" s="99" t="s">
         <v>1226</v>
-      </c>
-      <c r="F4" s="99" t="s">
-        <v>1227</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -16393,7 +16395,7 @@
         <v>894</v>
       </c>
       <c r="B5" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="C5">
         <f>분할_월_하체A!E28</f>
@@ -16416,7 +16418,7 @@
         <v>895</v>
       </c>
       <c r="B6" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="C6">
         <f>분할_화_가슴!E30</f>
@@ -16439,7 +16441,7 @@
         <v>896</v>
       </c>
       <c r="B7" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="C7">
         <f>분할_수_등!E22</f>
@@ -16462,7 +16464,7 @@
         <v>897</v>
       </c>
       <c r="B8" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="C8">
         <f>분할_목_어깨!E24</f>
@@ -16485,22 +16487,22 @@
         <v>898</v>
       </c>
       <c r="B9" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="C9">
         <f>분할_금_하체B!E27</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9">
         <f>분할_금_하체B!I27</f>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E9">
         <v>12</v>
       </c>
       <c r="F9">
         <f t="shared" si="0"/>
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1">
@@ -16508,7 +16510,7 @@
         <v>892</v>
       </c>
       <c r="B10" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="C10">
         <f>분할_토_가슴등!E23</f>
@@ -16541,11 +16543,11 @@
       <c r="B12" s="99"/>
       <c r="C12" s="99">
         <f>SUM(C5:C10)</f>
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D12" s="99">
         <f>SUM(D5:D10)</f>
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E12" s="99">
         <f>SUM(E5:E10)</f>
@@ -16553,23 +16555,23 @@
       </c>
       <c r="F12" s="99">
         <f>SUM(F5:F10)</f>
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="99" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="99" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="B15" s="99" t="s">
         <v>148</v>
       </c>
       <c r="C15" s="99" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -16580,40 +16582,40 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="B17">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="B18">
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="B19">
         <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -16621,43 +16623,43 @@
         <v>384</v>
       </c>
       <c r="B20">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>1241</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="B21">
         <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B22">
         <v>12</v>
       </c>
       <c r="C22" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B23">
         <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -16668,18 +16670,18 @@
         <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="B25">
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -16690,7 +16692,7 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -16701,29 +16703,29 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="B28">
         <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="B29">
         <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -16734,7 +16736,7 @@
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -16745,29 +16747,29 @@
         <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B32">
         <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="B33">
         <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -16778,7 +16780,7 @@
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -16789,7 +16791,7 @@
         <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -16798,46 +16800,46 @@
       </c>
       <c r="B36" s="99">
         <f>SUM(B16:B35)</f>
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="99" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="B37" s="99">
         <f>C12</f>
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
     </row>
   </sheetData>
@@ -17094,10 +17096,10 @@
         <v>3</v>
       </c>
       <c r="B19" s="135" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="C19" s="135" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="D19" s="136" t="s">
         <v>27</v>
@@ -17106,7 +17108,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="137" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="G19" s="135">
         <v>60</v>
@@ -17119,10 +17121,10 @@
         <v>9</v>
       </c>
       <c r="J19" s="138" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="K19" s="138" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15" customHeight="1">
@@ -17155,7 +17157,7 @@
         <v>1.7</v>
       </c>
       <c r="J20" s="134" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="K20" s="134"/>
       <c r="M20" t="s">
@@ -19862,7 +19864,7 @@
     <row r="2" spans="1:14">
       <c r="A2" t="str">
         <f>E27&amp;"세트 · 운동 "&amp;I27&amp;"분 + 웜업 12분 = "&amp;(I27+12)&amp;"분"</f>
-        <v>31세트 · 운동 79분 + 웜업 12분 = 91분</v>
+        <v>30세트 · 운동 76분 + 웜업 12분 = 88분</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -20340,7 +20342,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26" s="133" t="s">
         <v>350</v>
@@ -20353,10 +20355,10 @@
       </c>
       <c r="I26">
         <f t="shared" si="0"/>
-        <v>10.7</v>
+        <v>8</v>
       </c>
       <c r="J26" s="134" t="s">
-        <v>1203</v>
+        <v>1278</v>
       </c>
       <c r="K26" s="134" t="s">
         <v>1197</v>
@@ -20368,14 +20370,14 @@
       </c>
       <c r="E27" s="99">
         <f>SUM(E17:E26)</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F27" s="99"/>
       <c r="G27" s="99"/>
       <c r="H27" s="99"/>
       <c r="I27" s="99">
         <f>ROUND(SUM(I17:I26),0)</f>
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="30" customHeight="1"/>
@@ -20409,7 +20411,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="117" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -20425,7 +20427,7 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -20482,7 +20484,7 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="C9" t="s">
         <v>267</v>
@@ -20507,10 +20509,10 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J9" s="134" t="s">
+        <v>1206</v>
+      </c>
+      <c r="K9" s="134" t="s">
         <v>1207</v>
-      </c>
-      <c r="K9" s="134" t="s">
-        <v>1208</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="30">
@@ -20544,10 +20546,10 @@
         <v>2.5</v>
       </c>
       <c r="J10" s="134" t="s">
+        <v>1208</v>
+      </c>
+      <c r="K10" s="134" t="s">
         <v>1209</v>
-      </c>
-      <c r="K10" s="134" t="s">
-        <v>1210</v>
       </c>
       <c r="M10" t="s">
         <v>391</v>
@@ -20558,7 +20560,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="C11" t="s">
         <v>267</v>
@@ -20583,7 +20585,7 @@
         <v>9.5</v>
       </c>
       <c r="J11" s="134" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="K11" s="134"/>
       <c r="M11" t="s">
@@ -20620,7 +20622,7 @@
         <v>2.5</v>
       </c>
       <c r="J12" s="134" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="K12" s="134"/>
       <c r="M12" t="s">
@@ -20658,10 +20660,10 @@
         <v>9.5</v>
       </c>
       <c r="J13" s="134" t="s">
+        <v>1213</v>
+      </c>
+      <c r="K13" s="134" t="s">
         <v>1214</v>
-      </c>
-      <c r="K13" s="134" t="s">
-        <v>1215</v>
       </c>
       <c r="M13" t="s">
         <v>1109</v>
@@ -20697,10 +20699,10 @@
         <v>2.5</v>
       </c>
       <c r="J14" s="134" t="s">
+        <v>1215</v>
+      </c>
+      <c r="K14" s="134" t="s">
         <v>1216</v>
-      </c>
-      <c r="K14" s="134" t="s">
-        <v>1217</v>
       </c>
       <c r="M14" t="s">
         <v>659</v>
@@ -20736,7 +20738,7 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J15" s="134" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="K15" s="134" t="s">
         <v>410</v>
@@ -20809,11 +20811,11 @@
         <v>2.5</v>
       </c>
       <c r="J17" s="134" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="K17" s="134"/>
       <c r="M17" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -20848,7 +20850,7 @@
       <c r="J18" s="134"/>
       <c r="K18" s="134"/>
       <c r="M18" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15" customHeight="1">
@@ -20885,7 +20887,7 @@
       </c>
       <c r="K19" s="134"/>
       <c r="M19" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="30" customHeight="1">
@@ -20922,7 +20924,7 @@
       </c>
       <c r="K20" s="134"/>
       <c r="M20" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="30" customHeight="1">
@@ -20930,7 +20932,7 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="C21" t="s">
         <v>299</v>

--- a/운동프로그램_주6일분할_v21.xlsx
+++ b/운동프로그램_주6일분할_v21.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2bc197408547891/Desktop/운동/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4105" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB5E3654-5E14-4600-9749-F2FA60EC8F67}"/>
+  <xr:revisionPtr revIDLastSave="4116" documentId="11_6AF0B42629B6F5CFF7DAC05DB27E968F34409905" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6F54E9D-9ECE-4D18-A15F-F5E4DD39A413}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="976" firstSheet="7" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2455" uniqueCount="1281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="1282">
   <si>
     <t>복귀 버전 — 증량 및 판단 기준 (주 6회 · 2026-10-02 개편)</t>
   </si>
@@ -4043,9 +4043,6 @@
     </r>
   </si>
   <si>
-    <t>· 스쿼트 램프 · 몸풀기 5세트(위 표) — 약 12분.</t>
-  </si>
-  <si>
     <r>
       <t>운동</t>
     </r>
@@ -5097,9 +5094,6 @@
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>· 데드 램프 · 몸풀기 5세트(위 표) — 약 12분.</t>
-  </si>
-  <si>
     <t>증량표 E8 · 톱 1×5.</t>
   </si>
   <si>
@@ -7041,7 +7035,19 @@
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
-    <t>월~토 · 일요일 휴식 · 원본 Downloads\주6일_분할_프로그램.md + 월요일 트랩바 슈러그 3 · 불가리안(상체 숙여서) 3 · 레그 익스텐션 3→2 · 복귀판(v20)은 그대로 두고 한 달 뒤 돌아간다 · 금요일 시티드 레그 컬 4→3</t>
+    <t>· [2026-10-29 사용자 결정] 맨 앞, 신발 신기 전 맨발로 — 숏풋 5초 × 10(왼발 위주 · 발가락 펴고 엄지 뿌리를 뒤꿈치 쪽으로 당겨 아치만 세움) + 무릎 굽힌 종아리 스트레칭(가자미근) 왼쪽 2×45초 — 약 3분. 왼 아치 낮음 · 아치 세운 무릎 벽 테스트에서 왼쪽 1cm 못 닿음. 한 달 뒤 같은 조건 재측정(왼쪽이 닿거나 차이가 줄면 유지) + 오래 걸을 때 왼발 피로로 판정.</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 스쿼트 램프 · 몸풀기 5세트(위 표) — 약 12분(합계 웜업 15분).</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>· 데드 램프 · 몸풀기 5세트(위 표) — 약 12분(합계 웜업 15분).</t>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>월~토 · 일요일 휴식 · 원본 Downloads\주6일_분할_프로그램.md + 월요일 트랩바 슈러그 3 · 불가리안(상체 숙여서) 3 · 레그 익스텐션 3→2 · 복귀판(v20)은 그대로 두고 한 달 뒤 돌아간다 · 금요일 시티드 레그 컬 4→3 · 월·금 웜업에 숏풋 + 왼 종아리 스트레칭 3분</t>
     <phoneticPr fontId="29" type="noConversion"/>
   </si>
 </sst>
@@ -16362,12 +16368,12 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.75">
       <c r="A1" s="117" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -16375,19 +16381,19 @@
         <v>891</v>
       </c>
       <c r="B4" s="99" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C4" s="99" t="s">
         <v>148</v>
       </c>
       <c r="D4" s="99" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E4" s="99" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F4" s="99" t="s">
         <v>1224</v>
-      </c>
-      <c r="E4" s="99" t="s">
-        <v>1225</v>
-      </c>
-      <c r="F4" s="99" t="s">
-        <v>1226</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -16395,7 +16401,7 @@
         <v>894</v>
       </c>
       <c r="B5" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="C5">
         <f>분할_월_하체A!E28</f>
@@ -16406,11 +16412,11 @@
         <v>85</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F10" si="0">D5+E5</f>
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1">
@@ -16418,7 +16424,7 @@
         <v>895</v>
       </c>
       <c r="B6" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="C6">
         <f>분할_화_가슴!E30</f>
@@ -16441,7 +16447,7 @@
         <v>896</v>
       </c>
       <c r="B7" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="C7">
         <f>분할_수_등!E22</f>
@@ -16464,7 +16470,7 @@
         <v>897</v>
       </c>
       <c r="B8" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="C8">
         <f>분할_목_어깨!E24</f>
@@ -16487,7 +16493,7 @@
         <v>898</v>
       </c>
       <c r="B9" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="C9">
         <f>분할_금_하체B!E27</f>
@@ -16498,11 +16504,11 @@
         <v>76</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F9">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1">
@@ -16510,7 +16516,7 @@
         <v>892</v>
       </c>
       <c r="B10" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="C10">
         <f>분할_토_가슴등!E23</f>
@@ -16551,27 +16557,27 @@
       </c>
       <c r="E12" s="99">
         <f>SUM(E5:E10)</f>
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F12" s="99">
         <f>SUM(F5:F10)</f>
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="99" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="99" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="B15" s="99" t="s">
         <v>148</v>
       </c>
       <c r="C15" s="99" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -16582,40 +16588,40 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="B17">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="B18">
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="B19">
         <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -16626,40 +16632,40 @@
         <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="B21">
         <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="B22">
         <v>12</v>
       </c>
       <c r="C22" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B23">
         <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -16670,18 +16676,18 @@
         <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B25">
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -16692,7 +16698,7 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -16703,29 +16709,29 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B28">
         <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="B29">
         <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -16736,7 +16742,7 @@
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -16747,29 +16753,29 @@
         <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="B32">
         <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B33">
         <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -16780,7 +16786,7 @@
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -16791,7 +16797,7 @@
         <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -16805,7 +16811,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="99" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="B37" s="99">
         <f>C12</f>
@@ -16814,32 +16820,32 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
   </sheetData>
@@ -16875,8 +16881,8 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="str">
-        <f>E28&amp;"세트 · 운동 "&amp;I28&amp;"분 + 웜업 12분 = "&amp;(I28+12)&amp;"분"</f>
-        <v>36세트 · 운동 85분 + 웜업 12분 = 97분</v>
+        <f>E28&amp;"세트 · 운동 "&amp;I28&amp;"분 + 웜업 15분 = "&amp;(I28+15)&amp;"분"</f>
+        <v>36세트 · 운동 85분 + 웜업 15분 = 100분</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -16962,12 +16968,17 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>1084</v>
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>1279</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="99" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -16975,43 +16986,43 @@
         <v>253</v>
       </c>
       <c r="B16" s="131" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C16" s="131" t="s">
         <v>1086</v>
       </c>
-      <c r="C16" s="131" t="s">
+      <c r="D16" s="131" t="s">
         <v>1087</v>
       </c>
-      <c r="D16" s="131" t="s">
+      <c r="E16" s="131" t="s">
         <v>1088</v>
       </c>
-      <c r="E16" s="131" t="s">
+      <c r="F16" s="131" t="s">
         <v>1089</v>
       </c>
-      <c r="F16" s="131" t="s">
+      <c r="G16" s="131" t="s">
         <v>1090</v>
       </c>
-      <c r="G16" s="131" t="s">
+      <c r="H16" s="131" t="s">
         <v>1091</v>
       </c>
-      <c r="H16" s="131" t="s">
+      <c r="I16" s="131" t="s">
         <v>1092</v>
       </c>
-      <c r="I16" s="131" t="s">
+      <c r="J16" s="131" t="s">
         <v>1093</v>
       </c>
-      <c r="J16" s="131" t="s">
+      <c r="K16" s="131" t="s">
         <v>1094</v>
       </c>
-      <c r="K16" s="131" t="s">
+      <c r="L16" s="131" t="s">
         <v>1095</v>
       </c>
-      <c r="L16" s="131" t="s">
+      <c r="M16" s="131" t="s">
         <v>1096</v>
       </c>
-      <c r="M16" s="131" t="s">
+      <c r="N16" s="131" t="s">
         <v>1097</v>
-      </c>
-      <c r="N16" s="131" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="30">
@@ -17045,7 +17056,7 @@
         <v>17.5</v>
       </c>
       <c r="J17" s="134" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="K17" s="134" t="s">
         <v>899</v>
@@ -17085,7 +17096,7 @@
         <v>13</v>
       </c>
       <c r="J18" s="134" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="K18" s="134" t="s">
         <v>900</v>
@@ -17096,10 +17107,10 @@
         <v>3</v>
       </c>
       <c r="B19" s="135" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="C19" s="135" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="D19" s="136" t="s">
         <v>27</v>
@@ -17108,7 +17119,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="137" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="G19" s="135">
         <v>60</v>
@@ -17121,10 +17132,10 @@
         <v>9</v>
       </c>
       <c r="J19" s="138" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="K19" s="138" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15" customHeight="1">
@@ -17157,7 +17168,7 @@
         <v>1.7</v>
       </c>
       <c r="J20" s="134" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="K20" s="134"/>
       <c r="M20" t="s">
@@ -17194,7 +17205,7 @@
         <v>2.5</v>
       </c>
       <c r="J21" s="134" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="K21" s="134" t="s">
         <v>903</v>
@@ -17233,10 +17244,10 @@
         <v>8</v>
       </c>
       <c r="J22" s="134" t="s">
+        <v>1101</v>
+      </c>
+      <c r="K22" s="134" t="s">
         <v>1102</v>
-      </c>
-      <c r="K22" s="134" t="s">
-        <v>1103</v>
       </c>
       <c r="M22" t="s">
         <v>391</v>
@@ -17272,10 +17283,10 @@
         <v>11.9</v>
       </c>
       <c r="J23" s="134" t="s">
+        <v>1103</v>
+      </c>
+      <c r="K23" s="134" t="s">
         <v>1104</v>
-      </c>
-      <c r="K23" s="134" t="s">
-        <v>1105</v>
       </c>
       <c r="N23">
         <v>75</v>
@@ -17311,10 +17322,10 @@
         <v>9.6</v>
       </c>
       <c r="J24" s="134" t="s">
+        <v>1105</v>
+      </c>
+      <c r="K24" s="134" t="s">
         <v>1106</v>
-      </c>
-      <c r="K24" s="134" t="s">
-        <v>1107</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="30" customHeight="1">
@@ -17347,11 +17358,11 @@
         <v>1.7</v>
       </c>
       <c r="J25" s="134" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="K25" s="134"/>
       <c r="M25" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="30" customHeight="1">
@@ -17384,11 +17395,11 @@
         <v>3.3</v>
       </c>
       <c r="J26" s="134" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="K26" s="134"/>
       <c r="M26" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="30" customHeight="1">
@@ -17421,15 +17432,15 @@
         <v>6.5</v>
       </c>
       <c r="J27" s="134" t="s">
+        <v>1110</v>
+      </c>
+      <c r="K27" s="134" t="s">
         <v>1111</v>
-      </c>
-      <c r="K27" s="134" t="s">
-        <v>1112</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="30" customHeight="1">
       <c r="D28" s="99" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="E28" s="99">
         <f>SUM(E17:E27)</f>
@@ -17446,7 +17457,7 @@
     <row r="29" spans="1:14" ht="30" customHeight="1"/>
     <row r="30" spans="1:14" ht="30" customHeight="1">
       <c r="A30" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="30" customHeight="1"/>
@@ -17478,7 +17489,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="117" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -17489,7 +17500,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="107" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -17570,17 +17581,17 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="99" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -17588,43 +17599,43 @@
         <v>253</v>
       </c>
       <c r="B17" s="131" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C17" s="131" t="s">
         <v>1086</v>
       </c>
-      <c r="C17" s="131" t="s">
+      <c r="D17" s="131" t="s">
         <v>1087</v>
       </c>
-      <c r="D17" s="131" t="s">
+      <c r="E17" s="131" t="s">
         <v>1088</v>
       </c>
-      <c r="E17" s="131" t="s">
+      <c r="F17" s="131" t="s">
         <v>1089</v>
       </c>
-      <c r="F17" s="131" t="s">
+      <c r="G17" s="131" t="s">
         <v>1090</v>
       </c>
-      <c r="G17" s="131" t="s">
+      <c r="H17" s="131" t="s">
         <v>1091</v>
       </c>
-      <c r="H17" s="131" t="s">
+      <c r="I17" s="131" t="s">
         <v>1092</v>
       </c>
-      <c r="I17" s="131" t="s">
+      <c r="J17" s="131" t="s">
         <v>1093</v>
       </c>
-      <c r="J17" s="131" t="s">
+      <c r="K17" s="131" t="s">
         <v>1094</v>
       </c>
-      <c r="K17" s="131" t="s">
+      <c r="L17" s="131" t="s">
         <v>1095</v>
       </c>
-      <c r="L17" s="131" t="s">
+      <c r="M17" s="131" t="s">
         <v>1096</v>
       </c>
-      <c r="M17" s="131" t="s">
+      <c r="N17" s="131" t="s">
         <v>1097</v>
-      </c>
-      <c r="N17" s="131" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -17658,10 +17669,10 @@
         <v>15.3</v>
       </c>
       <c r="J18" s="134" t="s">
+        <v>1118</v>
+      </c>
+      <c r="K18" s="134" t="s">
         <v>1119</v>
-      </c>
-      <c r="K18" s="134" t="s">
-        <v>1120</v>
       </c>
       <c r="L18" s="133" t="s">
         <v>906</v>
@@ -17672,7 +17683,7 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="C19" t="s">
         <v>349</v>
@@ -17697,10 +17708,10 @@
         <v>10</v>
       </c>
       <c r="J19" s="134" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K19" s="134" t="s">
         <v>1122</v>
-      </c>
-      <c r="K19" s="134" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="30" customHeight="1">
@@ -17708,7 +17719,7 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="C20" t="s">
         <v>337</v>
@@ -17734,7 +17745,7 @@
       </c>
       <c r="J20" s="134"/>
       <c r="K20" s="134" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="30" customHeight="1">
@@ -17742,7 +17753,7 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="C21" t="s">
         <v>349</v>
@@ -17767,10 +17778,10 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="J21" s="134" t="s">
+        <v>1126</v>
+      </c>
+      <c r="K21" s="134" t="s">
         <v>1127</v>
-      </c>
-      <c r="K21" s="134" t="s">
-        <v>1128</v>
       </c>
       <c r="N21">
         <v>60</v>
@@ -17806,10 +17817,10 @@
         <v>1.7</v>
       </c>
       <c r="J22" s="134" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K22" s="134" t="s">
         <v>1129</v>
-      </c>
-      <c r="K22" s="134" t="s">
-        <v>1130</v>
       </c>
       <c r="M22" t="s">
         <v>391</v>
@@ -17820,7 +17831,7 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="C23" t="s">
         <v>345</v>
@@ -17845,7 +17856,7 @@
         <v>1.7</v>
       </c>
       <c r="J23" s="134" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="K23" s="134"/>
       <c r="M23" t="s">
@@ -17857,7 +17868,7 @@
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="C24" t="s">
         <v>345</v>
@@ -17882,7 +17893,7 @@
         <v>4.3</v>
       </c>
       <c r="J24" s="134" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="K24" s="134"/>
       <c r="M24" t="s">
@@ -17894,7 +17905,7 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="C25" t="s">
         <v>285</v>
@@ -17928,7 +17939,7 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="C26" t="s">
         <v>345</v>
@@ -17953,11 +17964,11 @@
         <v>3.5</v>
       </c>
       <c r="J26" s="134" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="K26" s="134"/>
       <c r="M26" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="30" customHeight="1">
@@ -17965,7 +17976,7 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="C27" t="s">
         <v>358</v>
@@ -17990,11 +18001,11 @@
         <v>5.3</v>
       </c>
       <c r="J27" s="134" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="K27" s="134"/>
       <c r="M27" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="30" customHeight="1">
@@ -18065,7 +18076,7 @@
     </row>
     <row r="30" spans="1:14" ht="30" customHeight="1">
       <c r="D30" s="99" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="E30" s="99">
         <f>SUM(E18:E29)</f>
@@ -18081,7 +18092,7 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
   </sheetData>
@@ -18112,7 +18123,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="117" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -18128,17 +18139,17 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="99" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -18146,43 +18157,43 @@
         <v>253</v>
       </c>
       <c r="B9" s="131" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C9" s="131" t="s">
         <v>1086</v>
       </c>
-      <c r="C9" s="131" t="s">
+      <c r="D9" s="131" t="s">
         <v>1087</v>
       </c>
-      <c r="D9" s="131" t="s">
+      <c r="E9" s="131" t="s">
         <v>1088</v>
       </c>
-      <c r="E9" s="131" t="s">
+      <c r="F9" s="131" t="s">
         <v>1089</v>
       </c>
-      <c r="F9" s="131" t="s">
+      <c r="G9" s="131" t="s">
         <v>1090</v>
       </c>
-      <c r="G9" s="131" t="s">
+      <c r="H9" s="131" t="s">
         <v>1091</v>
       </c>
-      <c r="H9" s="131" t="s">
+      <c r="I9" s="131" t="s">
         <v>1092</v>
       </c>
-      <c r="I9" s="131" t="s">
+      <c r="J9" s="131" t="s">
         <v>1093</v>
       </c>
-      <c r="J9" s="131" t="s">
+      <c r="K9" s="131" t="s">
         <v>1094</v>
       </c>
-      <c r="K9" s="131" t="s">
+      <c r="L9" s="131" t="s">
         <v>1095</v>
       </c>
-      <c r="L9" s="131" t="s">
+      <c r="M9" s="131" t="s">
         <v>1096</v>
       </c>
-      <c r="M9" s="131" t="s">
+      <c r="N9" s="131" t="s">
         <v>1097</v>
-      </c>
-      <c r="N9" s="131" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="30">
@@ -18190,7 +18201,7 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="C10" t="s">
         <v>267</v>
@@ -18215,10 +18226,10 @@
         <v>5.3</v>
       </c>
       <c r="J10" s="134" t="s">
+        <v>1144</v>
+      </c>
+      <c r="K10" s="134" t="s">
         <v>1145</v>
-      </c>
-      <c r="K10" s="134" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="30">
@@ -18252,10 +18263,10 @@
         <v>12.7</v>
       </c>
       <c r="J11" s="134" t="s">
+        <v>1146</v>
+      </c>
+      <c r="K11" s="134" t="s">
         <v>1147</v>
-      </c>
-      <c r="K11" s="134" t="s">
-        <v>1148</v>
       </c>
       <c r="L11" s="133" t="s">
         <v>904</v>
@@ -18266,7 +18277,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="C12" t="s">
         <v>282</v>
@@ -18291,10 +18302,10 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="J12" s="134" t="s">
+        <v>1149</v>
+      </c>
+      <c r="K12" s="134" t="s">
         <v>1150</v>
-      </c>
-      <c r="K12" s="134" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="90">
@@ -18314,7 +18325,7 @@
         <v>3</v>
       </c>
       <c r="F13" s="133" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G13">
         <v>60</v>
@@ -18327,10 +18338,10 @@
         <v>9</v>
       </c>
       <c r="J13" s="134" t="s">
+        <v>1152</v>
+      </c>
+      <c r="K13" s="134" t="s">
         <v>1153</v>
-      </c>
-      <c r="K13" s="134" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -18338,7 +18349,7 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="C14" t="s">
         <v>267</v>
@@ -18363,10 +18374,10 @@
         <v>5.8</v>
       </c>
       <c r="J14" s="134" t="s">
+        <v>1155</v>
+      </c>
+      <c r="K14" s="134" t="s">
         <v>1156</v>
-      </c>
-      <c r="K14" s="134" t="s">
-        <v>1157</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -18374,7 +18385,7 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C15" t="s">
         <v>269</v>
@@ -18399,10 +18410,10 @@
         <v>2.5</v>
       </c>
       <c r="J15" s="134" t="s">
+        <v>1158</v>
+      </c>
+      <c r="K15" s="134" t="s">
         <v>1159</v>
-      </c>
-      <c r="K15" s="134" t="s">
-        <v>1160</v>
       </c>
       <c r="M15" t="s">
         <v>391</v>
@@ -18439,10 +18450,10 @@
         <v>2.5</v>
       </c>
       <c r="J16" s="134" t="s">
+        <v>1160</v>
+      </c>
+      <c r="K16" s="134" t="s">
         <v>1161</v>
-      </c>
-      <c r="K16" s="134" t="s">
-        <v>1162</v>
       </c>
       <c r="M16" t="s">
         <v>391</v>
@@ -18453,7 +18464,7 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="C17" t="s">
         <v>269</v>
@@ -18478,7 +18489,7 @@
         <v>6.5</v>
       </c>
       <c r="J17" s="134" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="K17" s="134"/>
       <c r="M17" t="s">
@@ -18515,11 +18526,11 @@
         <v>1.7</v>
       </c>
       <c r="J18" s="134" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="K18" s="134"/>
       <c r="M18" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15" customHeight="1">
@@ -18552,11 +18563,11 @@
         <v>5</v>
       </c>
       <c r="J19" s="134" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="K19" s="134"/>
       <c r="M19" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="30" customHeight="1">
@@ -18621,13 +18632,13 @@
         <v>5</v>
       </c>
       <c r="J21" s="134" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="K21" s="134"/>
     </row>
     <row r="22" spans="1:13" ht="30" customHeight="1">
       <c r="D22" s="99" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="E22" s="99">
         <f>SUM(E10:E21)</f>
@@ -18644,12 +18655,12 @@
     <row r="23" spans="1:13" ht="30" customHeight="1"/>
     <row r="24" spans="1:13" ht="30" customHeight="1">
       <c r="A24" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="30" customHeight="1">
       <c r="A25" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="30" customHeight="1"/>
@@ -18685,7 +18696,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="117" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -18696,7 +18707,7 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="99" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -18740,17 +18751,17 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="99" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -18758,43 +18769,43 @@
         <v>253</v>
       </c>
       <c r="B14" s="131" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C14" s="131" t="s">
         <v>1086</v>
       </c>
-      <c r="C14" s="131" t="s">
+      <c r="D14" s="131" t="s">
         <v>1087</v>
       </c>
-      <c r="D14" s="131" t="s">
+      <c r="E14" s="131" t="s">
         <v>1088</v>
       </c>
-      <c r="E14" s="131" t="s">
+      <c r="F14" s="131" t="s">
         <v>1089</v>
       </c>
-      <c r="F14" s="131" t="s">
+      <c r="G14" s="131" t="s">
         <v>1090</v>
       </c>
-      <c r="G14" s="131" t="s">
+      <c r="H14" s="131" t="s">
         <v>1091</v>
       </c>
-      <c r="H14" s="131" t="s">
+      <c r="I14" s="131" t="s">
         <v>1092</v>
       </c>
-      <c r="I14" s="131" t="s">
+      <c r="J14" s="131" t="s">
         <v>1093</v>
       </c>
-      <c r="J14" s="131" t="s">
+      <c r="K14" s="131" t="s">
         <v>1094</v>
       </c>
-      <c r="K14" s="131" t="s">
+      <c r="L14" s="131" t="s">
         <v>1095</v>
       </c>
-      <c r="L14" s="131" t="s">
+      <c r="M14" s="131" t="s">
         <v>1096</v>
       </c>
-      <c r="M14" s="131" t="s">
+      <c r="N14" s="131" t="s">
         <v>1097</v>
-      </c>
-      <c r="N14" s="131" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -18827,10 +18838,10 @@
         <v>8</v>
       </c>
       <c r="J15" s="134" t="s">
+        <v>1171</v>
+      </c>
+      <c r="K15" s="134" t="s">
         <v>1172</v>
-      </c>
-      <c r="K15" s="134" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -18838,7 +18849,7 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="C16" t="s">
         <v>429</v>
@@ -18864,10 +18875,10 @@
         <v>11.5</v>
       </c>
       <c r="J16" s="134" t="s">
+        <v>1174</v>
+      </c>
+      <c r="K16" s="134" t="s">
         <v>1175</v>
-      </c>
-      <c r="K16" s="134" t="s">
-        <v>1176</v>
       </c>
       <c r="L16" s="133" t="s">
         <v>507</v>
@@ -18903,7 +18914,7 @@
         <v>3.3</v>
       </c>
       <c r="J17" s="134" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="K17" s="134" t="s">
         <v>410</v>
@@ -18917,7 +18928,7 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="C18" t="s">
         <v>354</v>
@@ -18942,7 +18953,7 @@
         <v>7.7</v>
       </c>
       <c r="J18" s="134" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="K18" s="134" t="s">
         <v>901</v>
@@ -18956,7 +18967,7 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="C19" t="s">
         <v>358</v>
@@ -18990,7 +19001,7 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C20" t="s">
         <v>429</v>
@@ -19050,10 +19061,10 @@
         <v>5.8</v>
       </c>
       <c r="J21" s="134" t="s">
+        <v>1181</v>
+      </c>
+      <c r="K21" s="134" t="s">
         <v>1182</v>
-      </c>
-      <c r="K21" s="134" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="30" customHeight="1">
@@ -19087,7 +19098,7 @@
       </c>
       <c r="J22" s="134"/>
       <c r="K22" s="134" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="30" customHeight="1">
@@ -19121,15 +19132,15 @@
         <v>7.7</v>
       </c>
       <c r="J23" s="134" t="s">
+        <v>1183</v>
+      </c>
+      <c r="K23" s="134" t="s">
         <v>1184</v>
-      </c>
-      <c r="K23" s="134" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="30" customHeight="1">
       <c r="D24" s="99" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="E24" s="99">
         <f>SUM(E15:E23)</f>
@@ -19858,18 +19869,18 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="117" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="str">
-        <f>E27&amp;"세트 · 운동 "&amp;I27&amp;"분 + 웜업 12분 = "&amp;(I27+12)&amp;"분"</f>
-        <v>30세트 · 운동 76분 + 웜업 12분 = 88분</v>
+        <f>E27&amp;"세트 · 운동 "&amp;I27&amp;"분 + 웜업 15분 = "&amp;(I27+15)&amp;"분"</f>
+        <v>30세트 · 운동 76분 + 웜업 15분 = 91분</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="107" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -19950,12 +19961,17 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>1188</v>
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>1280</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="99" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -19963,43 +19979,43 @@
         <v>253</v>
       </c>
       <c r="B16" s="131" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C16" s="131" t="s">
         <v>1086</v>
       </c>
-      <c r="C16" s="131" t="s">
+      <c r="D16" s="131" t="s">
         <v>1087</v>
       </c>
-      <c r="D16" s="131" t="s">
+      <c r="E16" s="131" t="s">
         <v>1088</v>
       </c>
-      <c r="E16" s="131" t="s">
+      <c r="F16" s="131" t="s">
         <v>1089</v>
       </c>
-      <c r="F16" s="131" t="s">
+      <c r="G16" s="131" t="s">
         <v>1090</v>
       </c>
-      <c r="G16" s="131" t="s">
+      <c r="H16" s="131" t="s">
         <v>1091</v>
       </c>
-      <c r="H16" s="131" t="s">
+      <c r="I16" s="131" t="s">
         <v>1092</v>
       </c>
-      <c r="I16" s="131" t="s">
+      <c r="J16" s="131" t="s">
         <v>1093</v>
       </c>
-      <c r="J16" s="131" t="s">
+      <c r="K16" s="131" t="s">
         <v>1094</v>
       </c>
-      <c r="K16" s="131" t="s">
+      <c r="L16" s="131" t="s">
         <v>1095</v>
       </c>
-      <c r="L16" s="131" t="s">
+      <c r="M16" s="131" t="s">
         <v>1096</v>
       </c>
-      <c r="M16" s="131" t="s">
+      <c r="N16" s="131" t="s">
         <v>1097</v>
-      </c>
-      <c r="N16" s="131" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -20033,10 +20049,10 @@
         <v>3.5</v>
       </c>
       <c r="J17" s="134" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="K17" s="134" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -20070,7 +20086,7 @@
         <v>7</v>
       </c>
       <c r="J18" s="134" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="K18" s="134"/>
     </row>
@@ -20105,10 +20121,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="J19" s="134" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="K19" s="134" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="30" customHeight="1">
@@ -20142,10 +20158,10 @@
         <v>10.7</v>
       </c>
       <c r="J20" s="134" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="K20" s="134" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="30" customHeight="1">
@@ -20153,7 +20169,7 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="C21" t="s">
         <v>384</v>
@@ -20165,7 +20181,7 @@
         <v>3</v>
       </c>
       <c r="F21" s="133" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G21">
         <v>60</v>
@@ -20179,7 +20195,7 @@
       </c>
       <c r="J21" s="134"/>
       <c r="K21" s="134" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="30" customHeight="1">
@@ -20212,7 +20228,7 @@
         <v>2.5</v>
       </c>
       <c r="J22" s="134" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="K22" s="134" t="s">
         <v>492</v>
@@ -20251,10 +20267,10 @@
         <v>8</v>
       </c>
       <c r="J23" s="134" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="K23" s="134" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="M23" t="s">
         <v>391</v>
@@ -20322,10 +20338,10 @@
         <v>9.6</v>
       </c>
       <c r="J25" s="134" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="K25" s="134" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="30" customHeight="1">
@@ -20333,7 +20349,7 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="C26" t="s">
         <v>384</v>
@@ -20358,15 +20374,15 @@
         <v>8</v>
       </c>
       <c r="J26" s="134" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="K26" s="134" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="30" customHeight="1">
       <c r="D27" s="99" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="E27" s="99">
         <f>SUM(E17:E26)</f>
@@ -20411,7 +20427,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="18.75">
       <c r="A1" s="117" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -20427,12 +20443,12 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="99" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -20440,43 +20456,43 @@
         <v>253</v>
       </c>
       <c r="B8" s="131" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C8" s="131" t="s">
         <v>1086</v>
       </c>
-      <c r="C8" s="131" t="s">
+      <c r="D8" s="131" t="s">
         <v>1087</v>
       </c>
-      <c r="D8" s="131" t="s">
+      <c r="E8" s="131" t="s">
         <v>1088</v>
       </c>
-      <c r="E8" s="131" t="s">
+      <c r="F8" s="131" t="s">
         <v>1089</v>
       </c>
-      <c r="F8" s="131" t="s">
+      <c r="G8" s="131" t="s">
         <v>1090</v>
       </c>
-      <c r="G8" s="131" t="s">
+      <c r="H8" s="131" t="s">
         <v>1091</v>
       </c>
-      <c r="H8" s="131" t="s">
+      <c r="I8" s="131" t="s">
         <v>1092</v>
       </c>
-      <c r="I8" s="131" t="s">
+      <c r="J8" s="131" t="s">
         <v>1093</v>
       </c>
-      <c r="J8" s="131" t="s">
+      <c r="K8" s="131" t="s">
         <v>1094</v>
       </c>
-      <c r="K8" s="131" t="s">
+      <c r="L8" s="131" t="s">
         <v>1095</v>
       </c>
-      <c r="L8" s="131" t="s">
+      <c r="M8" s="131" t="s">
         <v>1096</v>
       </c>
-      <c r="M8" s="131" t="s">
+      <c r="N8" s="131" t="s">
         <v>1097</v>
-      </c>
-      <c r="N8" s="131" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="30">
@@ -20484,7 +20500,7 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="C9" t="s">
         <v>267</v>
@@ -20509,10 +20525,10 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="J9" s="134" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="K9" s="134" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="30">
@@ -20546,10 +20562,10 @@
         <v>2.5</v>
       </c>
       <c r="J10" s="134" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="K10" s="134" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="M10" t="s">
         <v>391</v>
@@ -20560,7 +20576,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="C11" t="s">
         <v>267</v>
@@ -20585,7 +20601,7 @@
         <v>9.5</v>
       </c>
       <c r="J11" s="134" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="K11" s="134"/>
       <c r="M11" t="s">
@@ -20622,11 +20638,11 @@
         <v>2.5</v>
       </c>
       <c r="J12" s="134" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="K12" s="134"/>
       <c r="M12" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -20660,13 +20676,13 @@
         <v>9.5</v>
       </c>
       <c r="J13" s="134" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="K13" s="134" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="M13" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -20699,10 +20715,10 @@
         <v>2.5</v>
       </c>
       <c r="J14" s="134" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="K14" s="134" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="M14" t="s">
         <v>659</v>
@@ -20738,7 +20754,7 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="J15" s="134" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="K15" s="134" t="s">
         <v>410</v>
@@ -20778,7 +20794,7 @@
       </c>
       <c r="J16" s="134"/>
       <c r="K16" s="134" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -20811,11 +20827,11 @@
         <v>2.5</v>
       </c>
       <c r="J17" s="134" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="K17" s="134"/>
       <c r="M17" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -20850,7 +20866,7 @@
       <c r="J18" s="134"/>
       <c r="K18" s="134"/>
       <c r="M18" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15" customHeight="1">
@@ -20883,11 +20899,11 @@
         <v>1.7</v>
       </c>
       <c r="J19" s="134" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="K19" s="134"/>
       <c r="M19" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="30" customHeight="1">
@@ -20920,11 +20936,11 @@
         <v>5</v>
       </c>
       <c r="J20" s="134" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="K20" s="134"/>
       <c r="M20" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="30" customHeight="1">
@@ -20932,7 +20948,7 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="C21" t="s">
         <v>299</v>
@@ -20989,13 +21005,13 @@
         <v>5</v>
       </c>
       <c r="J22" s="134" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="K22" s="134"/>
     </row>
     <row r="23" spans="1:13" ht="30" customHeight="1">
       <c r="D23" s="99" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="E23" s="99">
         <f>SUM(E9:E22)</f>
